--- a/Unity/Assets/Config/Excel/CellChapterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CellChapterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,11 +38,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>ChapterName</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>RandomArea</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>章节名称</t>
   </si>
   <si>
@@ -50,24 +77,6 @@
   </si>
   <si>
     <t>章节关卡</t>
-  </si>
-  <si>
-    <t>ChapterName</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>RandomArea</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
   </si>
   <si>
     <t>初章</t>
@@ -119,7 +128,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +142,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -144,20 +159,6 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -708,152 +709,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -861,29 +862,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1076,8 +1080,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C4:F5" tableType="xml" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C4:F5" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="B1:E2" tableType="xml" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:E2" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Id" uniqueName="ID" dataDxfId="0">
       <xmlColumnPr mapId="3" xpath="/DateArea/date/@ID" xmlDataType="string"/>
@@ -1379,129 +1383,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="5" width="16.75" customWidth="1"/>
-    <col min="6" max="6" width="56.875" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="5" width="56.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B5" s="10">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B6" s="8">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B7" s="10">
         <v>4</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:5">
+      <c r="B8" s="10">
         <v>5</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>6</v>
+      <c r="C8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C7" s="9">
-        <v>2</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C8" s="7">
-        <v>3</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C9" s="9">
-        <v>4</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
-      <c r="C10" s="9">
-        <v>5</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1"/>
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1"/>
@@ -1510,8 +1525,6 @@
     <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
